--- a/AAII_Financials/Yearly/CHBAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CHBAY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>CHBAY</t>
   </si>
@@ -708,7 +708,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1824200</v>
+        <v>1761700</v>
       </c>
       <c r="E8" s="3">
         <v>1573800</v>
@@ -762,7 +762,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1824200</v>
+        <v>1761700</v>
       </c>
       <c r="E10" s="3">
         <v>1573800</v>
@@ -920,7 +920,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1109300</v>
+        <v>1046800</v>
       </c>
       <c r="E17" s="3">
         <v>972000</v>
@@ -1504,7 +1504,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>110200</v>
+        <v>119400</v>
       </c>
       <c r="E42" s="3">
         <v>194200</v>
@@ -1530,8 +1530,8 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>9200</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>5</v>
@@ -1585,7 +1585,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>166000</v>
+        <v>203200</v>
       </c>
       <c r="E45" s="3">
         <v>222500</v>
@@ -1612,7 +1612,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>28684300</v>
+        <v>28721500</v>
       </c>
       <c r="E46" s="3">
         <v>31491900</v>
@@ -1774,7 +1774,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2550600</v>
+        <v>2513400</v>
       </c>
       <c r="E52" s="3">
         <v>2693900</v>
@@ -1908,7 +1908,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>11280400</v>
+        <v>9787000</v>
       </c>
       <c r="E58" s="3">
         <v>10207000</v>
@@ -1935,7 +1935,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>171600</v>
+        <v>229000</v>
       </c>
       <c r="E59" s="3">
         <v>324100</v>
@@ -1962,7 +1962,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>123079700</v>
+        <v>121639100</v>
       </c>
       <c r="E60" s="3">
         <v>118344300</v>
@@ -1989,7 +1989,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11346800</v>
+        <v>12777200</v>
       </c>
       <c r="E61" s="3">
         <v>12317200</v>
@@ -2016,7 +2016,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2101200</v>
+        <v>2111500</v>
       </c>
       <c r="E62" s="3">
         <v>2035100</v>
@@ -2124,7 +2124,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>136803900</v>
+        <v>136803800</v>
       </c>
       <c r="E66" s="3">
         <v>133168400</v>
@@ -2668,7 +2668,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-2631400</v>
+        <v>-2563000</v>
       </c>
       <c r="E89" s="3">
         <v>2542200</v>
@@ -2829,7 +2829,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>167200</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -2937,7 +2937,7 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>2358900</v>
+        <v>2290500</v>
       </c>
       <c r="E100" s="3">
         <v>2456800</v>

--- a/AAII_Financials/Yearly/CHBAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CHBAY_YR_FIN.xlsx
@@ -2829,22 +2829,22 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>167200</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>143700</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>143600</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>134700</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>127600</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>111800</v>
       </c>
       <c r="J96" s="3">
         <v>108800</v>
